--- a/02_Inputs/Data/Charts/Module 8 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 8 - Datasets for Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="11_E743BBC76A7034957091EFBDE4F446C86DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0EEDA00-C8A1-4DED-B6E6-3126C1985040}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="11_E743BBC76A7034957091EFBDE4F446C86DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B525A5B-8508-488F-AFB3-AAC732F1AF25}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="23" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="20" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M8_C1_1" sheetId="5" r:id="rId1"/>
@@ -1630,7 +1630,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F99004-74EB-48D4-94BF-FFA90DF06068}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1759,7 +1759,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DA8E22-0FEF-4D4A-B2BC-19EE72C63E9F}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1888,7 +1888,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C5DE19-6443-49CB-ADB6-12B143AB356E}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2017,7 +2017,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6B2D8E-99D0-4B36-AC74-FDECB7C7195D}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2146,7 +2146,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF115116-EF61-4A38-A9F1-1CD110D60A5F}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2275,7 +2275,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B633B-9B00-4433-AC8A-867C102FA451}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2404,7 +2404,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F95F3-93CA-4870-BAFA-391EF63306CD}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3370,7 +3370,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78F8157-F157-46CB-A3C2-FE4E7FBBAF29}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -4308,7 +4308,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{058E9440-4D7D-479C-A2BC-F592E43F1710}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -19765,12 +19765,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20015,18 +20017,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B91EFA78-EAE5-417D-A782-785158D2872E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF9F0509-E5D2-4243-966D-365AE75FF403}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20034,5 +20034,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF9F0509-E5D2-4243-966D-365AE75FF403}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B91EFA78-EAE5-417D-A782-785158D2872E}"/>
 </file>